--- a/inputs/templates/TEMPLATE FONDO LIQUIDEZ FLEXIBLE DOLAR.xlsx
+++ b/inputs/templates/TEMPLATE FONDO LIQUIDEZ FLEXIBLE DOLAR.xlsx
@@ -541,7 +541,45 @@
         <v/>
       </c>
     </row>
-    <row r="6"/>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="C6">
+        <f>(B6/B5-1)/(A6-A5)*30</f>
+        <v/>
+      </c>
+      <c r="D6">
+        <f>+D5*(1+C6)</f>
+        <v/>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.0159</v>
+      </c>
+      <c r="H6">
+        <f>+G6+$S$148+$S$150+$S$152+$S$154+$S$156+$S$158</f>
+        <v/>
+      </c>
+      <c r="I6">
+        <f>+(H6/H5-1)/(F6-F5)*30</f>
+        <v/>
+      </c>
+      <c r="J6">
+        <f>+J5*(1+I6)</f>
+        <v/>
+      </c>
+      <c r="L6">
+        <f>+(K6/K5-1)/(F6-F5)*30</f>
+        <v/>
+      </c>
+      <c r="M6">
+        <f>+M5*(1+L6)</f>
+        <v/>
+      </c>
+    </row>
     <row r="7"/>
     <row r="8"/>
     <row r="9"/>
@@ -556,7 +594,7 @@
     <row r="18"/>
     <row r="19">
       <c r="AW19" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
     </row>
     <row r="20"/>

--- a/inputs/templates/TEMPLATE FONDO LIQUIDEZ FLEXIBLE DOLAR.xlsx
+++ b/inputs/templates/TEMPLATE FONDO LIQUIDEZ FLEXIBLE DOLAR.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW99"/>
+  <dimension ref="A1:AW19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,15 +463,7 @@
       <c r="B3" t="n">
         <v>26333.64</v>
       </c>
-      <c r="F3" s="1" t="n">
-        <v>46112</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
+      <c r="F3" s="1" t="n"/>
       <c r="K3" t="n">
         <v>1460.0275</v>
       </c>
@@ -597,86 +589,6 @@
         <v>46203</v>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
